--- a/FWA_Metric_to_Source_Mapping_2024.xlsx
+++ b/FWA_Metric_to_Source_Mapping_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metric to Source Mapping (2024)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source Datasets (2024)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric to Source Mapping (2024)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Datasets (2024)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,6 +552,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1080,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>3GPP / TelTech RAN Engineering</t>
+          <t>TelTech &amp; Comclark RAN Engineering (Referencing 3GPP TS 38.104)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1090,7 +1091,7 @@
       <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Modeled: = ROUNDUP(Target Subs @ 30% / 1,000, 0)
-Dimensioned strictly for 1,000 subscribers per BTS total across 3 sectors (~333 subs/sector).</t>
+Dimensioned for 1,000 subscribers per BTS total across 3 sectors (~333 subs/sector). Note: 3GPP TS 38.104 defines Band n50 RF specifications and 100MHz bandwidth, while the 1,000 subs/node capacity target is TelTech &amp; Comclark's RAN capacity planning standard.</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">

--- a/FWA_Metric_to_Source_Mapping_2024.xlsx
+++ b/FWA_Metric_to_Source_Mapping_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric to Source Mapping (2024)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Datasets (2024)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metric to Source Mapping (2024)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source Datasets (2024)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1271,6 +1271,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
